--- a/artfynd/A 63420-2025 artfynd.xlsx
+++ b/artfynd/A 63420-2025 artfynd.xlsx
@@ -4287,10 +4287,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132920042</v>
+        <v>132916495</v>
       </c>
       <c r="B33" t="n">
-        <v>92378</v>
+        <v>99130</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4298,34 +4298,38 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Backsjön, Backsjön, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>600735</v>
+        <v>600703</v>
       </c>
       <c r="R33" t="n">
-        <v>7035608</v>
+        <v>7035748</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4486,10 +4490,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132916495</v>
+        <v>132920042</v>
       </c>
       <c r="B35" t="n">
-        <v>99130</v>
+        <v>92378</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4497,38 +4501,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Backsjön, Backsjön, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>600703</v>
+        <v>600735</v>
       </c>
       <c r="R35" t="n">
-        <v>7035748</v>
+        <v>7035608</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -5173,45 +5173,49 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132916969</v>
+        <v>132916604</v>
       </c>
       <c r="B42" t="n">
-        <v>79333</v>
+        <v>99130</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Backsjön, Backsjön, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>600715</v>
+        <v>600709</v>
       </c>
       <c r="R42" t="n">
-        <v>7035784</v>
+        <v>7035785</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5270,32 +5274,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132915848</v>
+        <v>132916969</v>
       </c>
       <c r="B43" t="n">
-        <v>91881</v>
+        <v>79333</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5305,10 +5309,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>600644</v>
+        <v>600715</v>
       </c>
       <c r="R43" t="n">
-        <v>7035724</v>
+        <v>7035784</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5367,32 +5371,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132915856</v>
+        <v>132915848</v>
       </c>
       <c r="B44" t="n">
-        <v>79333</v>
+        <v>91881</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5402,10 +5406,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>600636</v>
+        <v>600644</v>
       </c>
       <c r="R44" t="n">
-        <v>7035716</v>
+        <v>7035724</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5464,49 +5468,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132916604</v>
+        <v>132915856</v>
       </c>
       <c r="B45" t="n">
-        <v>99130</v>
+        <v>79333</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Backsjön, Backsjön, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>600709</v>
+        <v>600636</v>
       </c>
       <c r="R45" t="n">
-        <v>7035785</v>
+        <v>7035716</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5662,49 +5662,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132915916</v>
+        <v>132920219</v>
       </c>
       <c r="B47" t="n">
-        <v>99130</v>
+        <v>80438</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Backsjön, Backsjön, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>600643</v>
+        <v>600717</v>
       </c>
       <c r="R47" t="n">
-        <v>7035720</v>
+        <v>7035620</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5763,7 +5759,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132920219</v>
+        <v>132916151</v>
       </c>
       <c r="B48" t="n">
         <v>80438</v>
@@ -5798,10 +5794,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>600717</v>
+        <v>600646</v>
       </c>
       <c r="R48" t="n">
-        <v>7035620</v>
+        <v>7035724</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5860,45 +5856,49 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132916151</v>
+        <v>132915916</v>
       </c>
       <c r="B49" t="n">
-        <v>80438</v>
+        <v>99130</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Backsjön, Backsjön, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>600646</v>
+        <v>600643</v>
       </c>
       <c r="R49" t="n">
-        <v>7035724</v>
+        <v>7035720</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>

--- a/artfynd/A 63420-2025 artfynd.xlsx
+++ b/artfynd/A 63420-2025 artfynd.xlsx
@@ -4388,50 +4388,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132919513</v>
+        <v>132920042</v>
       </c>
       <c r="B34" t="n">
-        <v>57955</v>
+        <v>92378</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Backsjön, Backsjön, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>600866</v>
+        <v>600735</v>
       </c>
       <c r="R34" t="n">
-        <v>7035660</v>
+        <v>7035608</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4490,45 +4485,50 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132920042</v>
+        <v>132919513</v>
       </c>
       <c r="B35" t="n">
-        <v>92378</v>
+        <v>57955</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Backsjön, Backsjön, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>600735</v>
+        <v>600866</v>
       </c>
       <c r="R35" t="n">
-        <v>7035608</v>
+        <v>7035660</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -5173,49 +5173,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132916604</v>
+        <v>132916969</v>
       </c>
       <c r="B42" t="n">
-        <v>99130</v>
+        <v>79333</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Backsjön, Backsjön, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>600709</v>
+        <v>600715</v>
       </c>
       <c r="R42" t="n">
-        <v>7035785</v>
+        <v>7035784</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5274,32 +5270,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132916969</v>
+        <v>132915848</v>
       </c>
       <c r="B43" t="n">
-        <v>79333</v>
+        <v>91881</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5309,10 +5305,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>600715</v>
+        <v>600644</v>
       </c>
       <c r="R43" t="n">
-        <v>7035784</v>
+        <v>7035724</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5371,32 +5367,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132915848</v>
+        <v>132915856</v>
       </c>
       <c r="B44" t="n">
-        <v>91881</v>
+        <v>79333</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5406,10 +5402,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>600644</v>
+        <v>600636</v>
       </c>
       <c r="R44" t="n">
-        <v>7035724</v>
+        <v>7035716</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5468,45 +5464,49 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132915856</v>
+        <v>132916604</v>
       </c>
       <c r="B45" t="n">
-        <v>79333</v>
+        <v>99130</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Backsjön, Backsjön, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>600636</v>
+        <v>600709</v>
       </c>
       <c r="R45" t="n">
-        <v>7035716</v>
+        <v>7035785</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>

--- a/artfynd/A 63420-2025 artfynd.xlsx
+++ b/artfynd/A 63420-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY58"/>
+  <dimension ref="A1:AY60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>55947895</v>
+        <v>105164104</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92605</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>898</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Backsjöskogen, Ång</t>
+          <t>Norrtannflo värdetrakt, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>600546.09704872</v>
+        <v>600756</v>
       </c>
       <c r="R2" t="n">
-        <v>7035705.905763941</v>
+        <v>7035583</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2015-06-30</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2015-06-30</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,12 +760,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Mikael Gudrunsson</t>
+          <t>Jennifer C. Johansson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Mikael Gudrunsson</t>
+          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -791,53 +776,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>55947894</v>
+        <v>105164111</v>
       </c>
       <c r="B3" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92605</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>898</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Backsjöskogen, Ång</t>
+          <t>Norrtannflo värdetrakt, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>600606.8163621476</v>
+        <v>600790</v>
       </c>
       <c r="R3" t="n">
-        <v>7035671.985188575</v>
+        <v>7035693</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -861,22 +841,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2015-06-30</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2015-06-30</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,12 +861,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Mikael Gudrunsson</t>
+          <t>Jennifer C. Johansson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Mikael Gudrunsson</t>
+          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -910,12 +880,7 @@
         <v>55947893</v>
       </c>
       <c r="B4" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -947,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>600606.8163621476</v>
+        <v>600607</v>
       </c>
       <c r="R4" t="n">
-        <v>7035671.985188575</v>
+        <v>7035672</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,19 +945,9 @@
           <t>2015-06-30</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2015-06-30</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,15 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>105164100</v>
+        <v>105164093</v>
       </c>
       <c r="B5" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1039,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1063,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>600694.2584405126</v>
+        <v>600656</v>
       </c>
       <c r="R5" t="n">
-        <v>7035615.616039534</v>
+        <v>7035651</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1096,19 +1046,9 @@
           <t>2022-10-11</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-10-11</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,15 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>105164117</v>
+        <v>105164097</v>
       </c>
       <c r="B6" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1155,21 +1090,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1179,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>600788.139997717</v>
+        <v>600702</v>
       </c>
       <c r="R6" t="n">
-        <v>7035795.945873889</v>
+        <v>7035649</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1212,19 +1147,9 @@
           <t>2022-10-11</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-10-11</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,15 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>105164112</v>
+        <v>105164101</v>
       </c>
       <c r="B7" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>600786.4301090416</v>
+        <v>600698</v>
       </c>
       <c r="R7" t="n">
-        <v>7035693.771371901</v>
+        <v>7035608</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1328,19 +1248,9 @@
           <t>2022-10-11</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-10-11</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1371,15 +1281,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>105164105</v>
+        <v>105164102</v>
       </c>
       <c r="B8" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,21 +1292,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1411,10 +1316,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>600755.5103410358</v>
+        <v>600735</v>
       </c>
       <c r="R8" t="n">
-        <v>7035593.359772623</v>
+        <v>7035576</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1444,19 +1349,9 @@
           <t>2022-10-11</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-10-11</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1487,15 +1382,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>105164115</v>
+        <v>105164103</v>
       </c>
       <c r="B9" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1503,21 +1393,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1527,10 +1417,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>600799.3345808615</v>
+        <v>600748</v>
       </c>
       <c r="R9" t="n">
-        <v>7035768.081893167</v>
+        <v>7035585</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1560,19 +1450,9 @@
           <t>2022-10-11</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-10-11</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1603,15 +1483,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>105164091</v>
+        <v>105164112</v>
       </c>
       <c r="B10" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1619,21 +1494,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1643,10 +1518,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>600754.5224522231</v>
+        <v>600786</v>
       </c>
       <c r="R10" t="n">
-        <v>7035681.56724647</v>
+        <v>7035694</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1676,19 +1551,9 @@
           <t>2022-10-11</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2022-10-11</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1719,15 +1584,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>105164097</v>
+        <v>105166426</v>
       </c>
       <c r="B11" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1759,10 +1619,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>600701.7421501988</v>
+        <v>600552</v>
       </c>
       <c r="R11" t="n">
-        <v>7035648.549509251</v>
+        <v>7035804</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1789,22 +1649,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2022-10-11</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-13</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2022-10-11</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-13</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1835,53 +1685,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>105164104</v>
+        <v>132915643</v>
       </c>
       <c r="B12" t="n">
-        <v>90052</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91974</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>898</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Norrtannflo värdetrakt, Ång</t>
+          <t>Backsjön, Backsjön, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>600755.8208174842</v>
+        <v>600600</v>
       </c>
       <c r="R12" t="n">
-        <v>7035583.515353665</v>
+        <v>7035707</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1905,22 +1750,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2022-10-11</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2022-10-11</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1935,31 +1770,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Jennifer C. Johansson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering Y-län</t>
-        </is>
-      </c>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>105164109</v>
+        <v>132919682</v>
       </c>
       <c r="B13" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91974</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1967,37 +1793,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Norrtannflo värdetrakt, Ång</t>
+          <t>Backsjön, Backsjön, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>600772.148918134</v>
+        <v>600803</v>
       </c>
       <c r="R13" t="n">
-        <v>7035634.644855526</v>
+        <v>7035645</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2021,22 +1847,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2022-10-11</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2022-10-11</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2051,31 +1867,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Jennifer C. Johansson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering Y-län</t>
-        </is>
-      </c>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>105164113</v>
+        <v>105164095</v>
       </c>
       <c r="B14" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2083,21 +1890,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2107,10 +1914,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>600798.9683638336</v>
+        <v>600662</v>
       </c>
       <c r="R14" t="n">
-        <v>7035722.83271997</v>
+        <v>7035644</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2140,24 +1947,14 @@
           <t>2022-10-11</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2022-10-11</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Riklig</t>
+          <t>Gammalt och torkat</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2188,15 +1985,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>105164101</v>
+        <v>105164107</v>
       </c>
       <c r="B15" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2204,21 +1996,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2228,10 +2020,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>600698.5449786631</v>
+        <v>600738</v>
       </c>
       <c r="R15" t="n">
-        <v>7035607.688684187</v>
+        <v>7035609</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2261,19 +2053,9 @@
           <t>2022-10-11</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2022-10-11</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2304,15 +2086,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>105164099</v>
+        <v>132920042</v>
       </c>
       <c r="B16" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92406</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2320,37 +2097,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>1209</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Norrtannflo värdetrakt, Ång</t>
+          <t>Backsjön, Backsjön, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>600688.8783338004</v>
+        <v>600735</v>
       </c>
       <c r="R16" t="n">
-        <v>7035629.779689988</v>
+        <v>7035608</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2374,27 +2151,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2022-10-11</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2022-10-11</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>3 fåglar</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2409,31 +2171,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Jennifer C. Johansson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering Y-län</t>
-        </is>
-      </c>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>105164098</v>
+        <v>105164109</v>
       </c>
       <c r="B17" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2441,21 +2194,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2465,10 +2218,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>600690.907134819</v>
+        <v>600772</v>
       </c>
       <c r="R17" t="n">
-        <v>7035636.562311069</v>
+        <v>7035634</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2498,19 +2251,9 @@
           <t>2022-10-11</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2022-10-11</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2541,15 +2284,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>105164103</v>
+        <v>105164116</v>
       </c>
       <c r="B18" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2557,21 +2295,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2581,10 +2319,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>600748.5810202428</v>
+        <v>600799</v>
       </c>
       <c r="R18" t="n">
-        <v>7035585.526626751</v>
+        <v>7035795</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2614,19 +2352,9 @@
           <t>2022-10-11</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2022-10-11</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2660,12 +2388,7 @@
         <v>105164110</v>
       </c>
       <c r="B19" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2697,10 +2420,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>600794.4565874874</v>
+        <v>600794</v>
       </c>
       <c r="R19" t="n">
-        <v>7035681.035359465</v>
+        <v>7035681</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2730,19 +2453,9 @@
           <t>2022-10-11</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2022-10-11</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2773,53 +2486,48 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>105164111</v>
+        <v>132915402</v>
       </c>
       <c r="B20" t="n">
-        <v>90052</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91937</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>898</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Norrtannflo värdetrakt, Ång</t>
+          <t>Backsjön, Backsjön, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>600790.0428401257</v>
+        <v>600597</v>
       </c>
       <c r="R20" t="n">
-        <v>7035692.989544163</v>
+        <v>7035677</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2843,22 +2551,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2022-10-11</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2022-10-11</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2873,69 +2571,60 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Jennifer C. Johansson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering Y-län</t>
-        </is>
-      </c>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>105164093</v>
+        <v>132915848</v>
       </c>
       <c r="B21" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91937</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Norrtannflo värdetrakt, Ång</t>
+          <t>Backsjön, Backsjön, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>600655.9122912308</v>
+        <v>600644</v>
       </c>
       <c r="R21" t="n">
-        <v>7035651.136363965</v>
+        <v>7035724</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2959,22 +2648,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2022-10-11</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2022-10-11</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2989,66 +2668,58 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Jennifer C. Johansson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering Y-län</t>
-        </is>
-      </c>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>105164096</v>
+        <v>104505435</v>
       </c>
       <c r="B22" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Norrtannflo värdetrakt, Ång</t>
+          <t>Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>600688.6776535599</v>
+        <v>600696</v>
       </c>
       <c r="R22" t="n">
-        <v>7035650.377262128</v>
+        <v>7035968</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3075,22 +2746,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2022-10-11</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-06</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2022-10-11</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-06</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3105,53 +2771,44 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Jennifer C. Johansson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering Y-län</t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>105164092</v>
+        <v>105164090</v>
       </c>
       <c r="B23" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3161,10 +2818,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>600646.5984991568</v>
+        <v>600745</v>
       </c>
       <c r="R23" t="n">
-        <v>7035662.040622448</v>
+        <v>7035831</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3194,19 +2851,14 @@
           <t>2022-10-11</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2022-10-11</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Riklig</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3237,37 +2889,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>105164114</v>
+        <v>105164108</v>
       </c>
       <c r="B24" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3277,10 +2924,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>600806.8780878383</v>
+        <v>600747</v>
       </c>
       <c r="R24" t="n">
-        <v>7035728.009210156</v>
+        <v>7035611</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3310,19 +2957,14 @@
           <t>2022-10-11</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2022-10-11</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Riklig</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3353,37 +2995,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>105164102</v>
+        <v>105164113</v>
       </c>
       <c r="B25" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3393,10 +3030,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>600734.5247419212</v>
+        <v>600799</v>
       </c>
       <c r="R25" t="n">
-        <v>7035576.124986785</v>
+        <v>7035723</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3426,19 +3063,14 @@
           <t>2022-10-11</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2022-10-11</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Riklig</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3469,37 +3101,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>105164094</v>
+        <v>105164115</v>
       </c>
       <c r="B26" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3509,10 +3136,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>600656.8084269345</v>
+        <v>600799</v>
       </c>
       <c r="R26" t="n">
-        <v>7035651.164599424</v>
+        <v>7035768</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3542,19 +3169,9 @@
           <t>2022-10-11</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2022-10-11</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3585,19 +3202,14 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>105164108</v>
+        <v>132915856</v>
       </c>
       <c r="B27" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79373</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -3621,17 +3233,17 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Norrtannflo värdetrakt, Ång</t>
+          <t>Backsjön, Backsjön, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>600747.3144781388</v>
+        <v>600636</v>
       </c>
       <c r="R27" t="n">
-        <v>7035611.465882406</v>
+        <v>7035716</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3655,27 +3267,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2022-10-11</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2022-10-11</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Riklig</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3690,35 +3287,26 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Jennifer C. Johansson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering Y-län</t>
-        </is>
-      </c>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>105164090</v>
+        <v>132916969</v>
       </c>
       <c r="B28" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79373</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -3742,17 +3330,17 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Norrtannflo värdetrakt, Ång</t>
+          <t>Backsjön, Backsjön, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>600744.4183323164</v>
+        <v>600715</v>
       </c>
       <c r="R28" t="n">
-        <v>7035831.293463509</v>
+        <v>7035784</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3776,27 +3364,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2022-10-11</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2022-10-11</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Riklig</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3811,31 +3384,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Jennifer C. Johansson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering Y-län</t>
-        </is>
-      </c>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>105164095</v>
+        <v>132919520</v>
       </c>
       <c r="B29" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79373</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3843,37 +3407,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Norrtannflo värdetrakt, Ång</t>
+          <t>Backsjön, Backsjön, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>600661.9627650453</v>
+        <v>600866</v>
       </c>
       <c r="R29" t="n">
-        <v>7035644.160455705</v>
+        <v>7035660</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3897,27 +3461,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2022-10-11</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2022-10-11</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Gammalt och torkat</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3932,31 +3481,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Jennifer C. Johansson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering Y-län</t>
-        </is>
-      </c>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>105164107</v>
+        <v>132919915</v>
       </c>
       <c r="B30" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79373</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3964,37 +3504,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Norrtannflo värdetrakt, Ång</t>
+          <t>Backsjön, Backsjön, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>600738.4094481401</v>
+        <v>600779</v>
       </c>
       <c r="R30" t="n">
-        <v>7035609.393404054</v>
+        <v>7035617</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4018,22 +3558,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2022-10-11</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2022-10-11</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4048,31 +3578,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Jennifer C. Johansson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering Y-län</t>
-        </is>
-      </c>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>105164116</v>
+        <v>105164092</v>
       </c>
       <c r="B31" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4080,21 +3601,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1312</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4104,10 +3625,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>600798.9354983487</v>
+        <v>600647</v>
       </c>
       <c r="R31" t="n">
-        <v>7035794.942830876</v>
+        <v>7035662</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4137,19 +3658,9 @@
           <t>2022-10-11</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2022-10-11</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4180,10 +3691,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132915530</v>
+        <v>105164091</v>
       </c>
       <c r="B32" t="n">
-        <v>57958</v>
+        <v>79946</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4191,42 +3702,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Backsjön, Backsjön, Ång</t>
+          <t>Norrtannflo värdetrakt, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>600593</v>
+        <v>600754</v>
       </c>
       <c r="R32" t="n">
-        <v>7035682</v>
+        <v>7035681</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4250,17 +3756,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2022-10-11</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Färska ringhack, tall</t>
+          <t>2022-10-11</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4275,60 +3776,64 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Jennifer C. Johansson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr"/>
+          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132920042</v>
+        <v>55947895</v>
       </c>
       <c r="B33" t="n">
-        <v>92388</v>
+        <v>80432</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Backsjön, Backsjön, Ång</t>
+          <t>Backsjöskogen, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>600735</v>
+        <v>600546</v>
       </c>
       <c r="R33" t="n">
-        <v>7035608</v>
+        <v>7035706</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4352,12 +3857,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2015-06-30</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2015-06-30</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4372,22 +3877,26 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mikael Gudrunsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY33" t="inlineStr"/>
+          <t>Mikael Gudrunsson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132919513</v>
+        <v>104505700</v>
       </c>
       <c r="B34" t="n">
-        <v>57955</v>
+        <v>80432</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4395,42 +3904,38 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="K34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Backsjön, Backsjön, Ång</t>
+          <t>Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>600866</v>
+        <v>600798</v>
       </c>
       <c r="R34" t="n">
-        <v>7035660</v>
+        <v>7035841</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4454,12 +3959,17 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2022-11-06</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2022-11-06</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4474,64 +3984,61 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132916495</v>
+        <v>104505737</v>
       </c>
       <c r="B35" t="n">
-        <v>99140</v>
+        <v>80432</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Backsjön, Backsjön, Ång</t>
+          <t>Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>600703</v>
+        <v>600803</v>
       </c>
       <c r="R35" t="n">
-        <v>7035748</v>
+        <v>7035850</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4555,12 +4062,17 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2022-11-06</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2022-11-06</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4575,64 +4087,60 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132915804</v>
+        <v>105164094</v>
       </c>
       <c r="B36" t="n">
-        <v>99140</v>
+        <v>80432</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Backsjön, Backsjön, Ång</t>
+          <t>Norrtannflo värdetrakt, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>600627</v>
+        <v>600657</v>
       </c>
       <c r="R36" t="n">
-        <v>7035716</v>
+        <v>7035651</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4656,12 +4164,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2022-10-11</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2022-10-11</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4676,22 +4184,26 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Jennifer C. Johansson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr"/>
+          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132916664</v>
+        <v>105164096</v>
       </c>
       <c r="B37" t="n">
-        <v>80439</v>
+        <v>80432</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4719,17 +4231,17 @@
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Backsjön, Backsjön, Ång</t>
+          <t>Norrtannflo värdetrakt, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>600708</v>
+        <v>600689</v>
       </c>
       <c r="R37" t="n">
-        <v>7035786</v>
+        <v>7035651</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4753,12 +4265,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2022-10-11</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2022-10-11</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4773,22 +4285,26 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Jennifer C. Johansson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr"/>
+          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132920340</v>
+        <v>105164098</v>
       </c>
       <c r="B38" t="n">
-        <v>80439</v>
+        <v>80432</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4816,17 +4332,17 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Backsjön, Backsjön, Ång</t>
+          <t>Norrtannflo värdetrakt, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>600719</v>
+        <v>600691</v>
       </c>
       <c r="R38" t="n">
         <v>7035636</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4850,12 +4366,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2022-10-11</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2022-10-11</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4870,22 +4386,26 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Jennifer C. Johansson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY38" t="inlineStr"/>
+          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132919915</v>
+        <v>105164100</v>
       </c>
       <c r="B39" t="n">
-        <v>79334</v>
+        <v>80432</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4893,37 +4413,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Backsjön, Backsjön, Ång</t>
+          <t>Norrtannflo värdetrakt, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>600779</v>
+        <v>600694</v>
       </c>
       <c r="R39" t="n">
-        <v>7035617</v>
+        <v>7035615</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4947,12 +4467,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2022-10-11</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2022-10-11</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4967,22 +4487,26 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Jennifer C. Johansson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr"/>
+          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132915582</v>
+        <v>105164114</v>
       </c>
       <c r="B40" t="n">
-        <v>80439</v>
+        <v>80432</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5010,17 +4534,17 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Backsjön, Backsjön, Ång</t>
+          <t>Norrtannflo värdetrakt, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>600599</v>
+        <v>600807</v>
       </c>
       <c r="R40" t="n">
-        <v>7035708</v>
+        <v>7035728</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5044,12 +4568,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2022-10-11</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2022-10-11</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5064,22 +4588,26 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Jennifer C. Johansson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY40" t="inlineStr"/>
+          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132915643</v>
+        <v>105164117</v>
       </c>
       <c r="B41" t="n">
-        <v>91928</v>
+        <v>80432</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5087,37 +4615,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Backsjön, Backsjön, Ång</t>
+          <t>Norrtannflo värdetrakt, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>600600</v>
+        <v>600788</v>
       </c>
       <c r="R41" t="n">
-        <v>7035707</v>
+        <v>7035796</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5141,12 +4669,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2022-10-11</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2022-10-11</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5161,22 +4689,26 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Jennifer C. Johansson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY41" t="inlineStr"/>
+          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132916969</v>
+        <v>132915395</v>
       </c>
       <c r="B42" t="n">
-        <v>79334</v>
+        <v>80488</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5184,21 +4716,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5208,10 +4740,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>600715</v>
+        <v>600597</v>
       </c>
       <c r="R42" t="n">
-        <v>7035784</v>
+        <v>7035677</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5270,49 +4802,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132916604</v>
+        <v>132915582</v>
       </c>
       <c r="B43" t="n">
-        <v>99140</v>
+        <v>80488</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Backsjön, Backsjön, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>600709</v>
+        <v>600599</v>
       </c>
       <c r="R43" t="n">
-        <v>7035785</v>
+        <v>7035708</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5371,32 +4899,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132915848</v>
+        <v>132916151</v>
       </c>
       <c r="B44" t="n">
-        <v>91891</v>
+        <v>80488</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5406,7 +4934,7 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>600644</v>
+        <v>600646</v>
       </c>
       <c r="R44" t="n">
         <v>7035724</v>
@@ -5468,10 +4996,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132915856</v>
+        <v>132916664</v>
       </c>
       <c r="B45" t="n">
-        <v>79334</v>
+        <v>80488</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5479,21 +5007,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5503,10 +5031,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>600636</v>
+        <v>600708</v>
       </c>
       <c r="R45" t="n">
-        <v>7035716</v>
+        <v>7035786</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5565,10 +5093,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132919682</v>
+        <v>132920219</v>
       </c>
       <c r="B46" t="n">
-        <v>91928</v>
+        <v>80488</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5576,21 +5104,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5600,10 +5128,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>600803</v>
+        <v>600717</v>
       </c>
       <c r="R46" t="n">
-        <v>7035645</v>
+        <v>7035620</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5662,10 +5190,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132920219</v>
+        <v>132920340</v>
       </c>
       <c r="B47" t="n">
-        <v>80439</v>
+        <v>80488</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5697,10 +5225,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>600717</v>
+        <v>600719</v>
       </c>
       <c r="R47" t="n">
-        <v>7035620</v>
+        <v>7035636</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5759,45 +5287,50 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132916151</v>
+        <v>132919513</v>
       </c>
       <c r="B48" t="n">
-        <v>80439</v>
+        <v>57972</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Backsjön, Backsjön, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>600646</v>
+        <v>600866</v>
       </c>
       <c r="R48" t="n">
-        <v>7035724</v>
+        <v>7035660</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5856,37 +5389,38 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132915916</v>
+        <v>132915530</v>
       </c>
       <c r="B49" t="n">
-        <v>99140</v>
+        <v>57975</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>5</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5895,10 +5429,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>600643</v>
+        <v>600593</v>
       </c>
       <c r="R49" t="n">
-        <v>7035720</v>
+        <v>7035682</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5931,6 +5465,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5960,7 +5499,7 @@
         <v>132920320</v>
       </c>
       <c r="B50" t="n">
-        <v>57958</v>
+        <v>57975</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6064,10 +5603,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132920398</v>
+        <v>132920700</v>
       </c>
       <c r="B51" t="n">
-        <v>56522</v>
+        <v>57975</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6075,27 +5614,27 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>206004</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -6104,10 +5643,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>600712</v>
+        <v>600660</v>
       </c>
       <c r="R51" t="n">
-        <v>7035629</v>
+        <v>7035679</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -6140,6 +5679,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Färska ringhack, gran</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6166,10 +5710,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132919520</v>
+        <v>132920770</v>
       </c>
       <c r="B52" t="n">
-        <v>79334</v>
+        <v>57975</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6177,34 +5721,39 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Backsjön, Backsjön, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>600866</v>
+        <v>600644</v>
       </c>
       <c r="R52" t="n">
-        <v>7035660</v>
+        <v>7035688</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6237,6 +5786,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Färska ringhack, gran</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6263,37 +5817,38 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132920443</v>
+        <v>132919875</v>
       </c>
       <c r="B53" t="n">
-        <v>99140</v>
+        <v>57162</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>8</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6302,10 +5857,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>600690</v>
+        <v>600788</v>
       </c>
       <c r="R53" t="n">
-        <v>7035617</v>
+        <v>7035632</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6364,10 +5919,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132920700</v>
+        <v>105164099</v>
       </c>
       <c r="B54" t="n">
-        <v>57958</v>
+        <v>58114</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6375,42 +5930,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Backsjön, Backsjön, Ång</t>
+          <t>Norrtannflo värdetrakt, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>600660</v>
+        <v>600689</v>
       </c>
       <c r="R54" t="n">
-        <v>7035679</v>
+        <v>7035630</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6434,17 +5984,17 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2022-10-11</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2022-10-11</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Färska ringhack, gran</t>
+          <t>3 fåglar</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6459,22 +6009,26 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Jennifer C. Johansson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY54" t="inlineStr"/>
+          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132920770</v>
+        <v>132920398</v>
       </c>
       <c r="B55" t="n">
-        <v>57958</v>
+        <v>56539</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6482,27 +6036,27 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>206004</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -6511,10 +6065,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>600644</v>
+        <v>600712</v>
       </c>
       <c r="R55" t="n">
-        <v>7035688</v>
+        <v>7035629</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6547,11 +6101,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Färska ringhack, gran</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6578,45 +6127,49 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132915395</v>
+        <v>132915804</v>
       </c>
       <c r="B56" t="n">
-        <v>80439</v>
+        <v>99195</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Backsjön, Backsjön, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>600597</v>
+        <v>600627</v>
       </c>
       <c r="R56" t="n">
-        <v>7035677</v>
+        <v>7035716</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6675,45 +6228,49 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132915402</v>
+        <v>132915916</v>
       </c>
       <c r="B57" t="n">
-        <v>91891</v>
+        <v>99195</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Backsjön, Backsjön, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>600597</v>
+        <v>600643</v>
       </c>
       <c r="R57" t="n">
-        <v>7035677</v>
+        <v>7035720</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6772,38 +6329,37 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132919875</v>
+        <v>132916495</v>
       </c>
       <c r="B58" t="n">
-        <v>57145</v>
+        <v>99195</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -6812,10 +6368,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>600788</v>
+        <v>600703</v>
       </c>
       <c r="R58" t="n">
-        <v>7035632</v>
+        <v>7035748</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6871,6 +6427,208 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>132916604</v>
+      </c>
+      <c r="B59" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Backsjön, Backsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>600709</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7035785</v>
+      </c>
+      <c r="S59" t="n">
+        <v>15</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>132920443</v>
+      </c>
+      <c r="B60" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Backsjön, Backsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>600690</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7035617</v>
+      </c>
+      <c r="S60" t="n">
+        <v>15</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 63420-2025 artfynd.xlsx
+++ b/artfynd/A 63420-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY60"/>
+  <dimension ref="A1:AZ60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105164104</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105164111</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55947893</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105164093</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105164097</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105164101</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105164102</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1480,6 +1520,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105164103</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1581,6 +1626,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105164112</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1682,6 +1732,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105166426</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1779,6 +1834,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132915643</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1876,6 +1936,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132919682</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1982,6 +2047,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105164095</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2083,6 +2153,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105164107</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2180,6 +2255,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132920042</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2281,6 +2361,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105164109</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2382,6 +2467,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105164116</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2483,6 +2573,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105164110</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2580,6 +2675,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132915402</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2677,6 +2777,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132915848</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2780,6 +2885,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104505435</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2886,6 +2996,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105164090</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2992,6 +3107,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105164108</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3098,6 +3218,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105164113</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3199,6 +3324,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105164115</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3296,6 +3426,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132915856</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3393,6 +3528,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132916969</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3490,6 +3630,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132919520</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3587,6 +3732,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132919915</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3688,6 +3838,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105164092</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3789,6 +3944,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105164091</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3890,6 +4050,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55947895</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3993,6 +4158,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104505700</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4096,6 +4266,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104505737</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4197,6 +4372,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105164094</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4298,6 +4478,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105164096</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4399,6 +4584,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105164098</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4500,6 +4690,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105164100</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4601,6 +4796,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105164114</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4702,6 +4902,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105164117</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4799,6 +5004,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132915395</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4896,6 +5106,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132915582</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4993,6 +5208,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132916151</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5090,6 +5310,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132916664</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5187,6 +5412,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132920219</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5284,6 +5514,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132920340</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5386,6 +5621,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132919513</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5493,6 +5733,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132915530</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5600,6 +5845,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132920320</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5707,6 +5957,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132920700</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5814,6 +6069,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132920770</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5916,6 +6176,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132919875</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6022,6 +6287,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105164099</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6124,6 +6394,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132920398</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6225,6 +6500,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132915804</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6326,6 +6606,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132915916</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6427,6 +6712,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132916495</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6528,6 +6818,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132916604</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6629,8 +6924,74 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132920443</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>